--- a/data/trans_dic/KIDM_C_3_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_3_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -648,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,27; 10,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,76; 23,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,42; 12,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,22; 9,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,9; 7,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,5; 17,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,13; 13,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,37; 9,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,15; 7,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,93; 18,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,57; 11,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,88; 7,46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>12-15</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -788,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,63; 8,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,64; 17,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,56; 14,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,36; 7,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,15; 7,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,54; 15,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,55; 15,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,96; 6,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,4; 15,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,93; 13,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,9; 3,85</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8-11</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -928,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -996,358 +997,76 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 10,83</t>
+          <t>3,53; 7,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,24; 24,08</t>
+          <t>11,93; 18,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 12,04</t>
+          <t>6,5; 11,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,62</t>
+          <t>1,71; 6,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 7,5</t>
+          <t>2,6; 6,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,52; 17,46</t>
+          <t>8,87; 14,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 13,23</t>
+          <t>7,49; 12,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 9,44</t>
+          <t>0,79; 3,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,5</t>
+          <t>3,41; 6,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,88; 18,62</t>
+          <t>11,33; 15,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,41; 11,39</t>
+          <t>7,86; 11,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,17</t>
+          <t>1,76; 4,46</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2,9; 8,17</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8,73; 17,11</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6,21; 14,38</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 6,92</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,3; 7,29</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7,69; 15,27</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7,45; 15,29</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,44</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3,03; 6,43</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>9,14; 14,62</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7,81; 13,31</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,9; 3,81</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>13,42%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>3,58; 7,76</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12,01; 18,83</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6,9; 12,01</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1,7; 6,96</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,46; 6,11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,02; 14,99</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,55; 13,27</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,84; 4,15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3,57; 6,3</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11,31; 15,76</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7,83; 11,52</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,63; 4,17</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
@@ -1356,4 +1075,786 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6848</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26843</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15191</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4935</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19134</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16217</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3984</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>11783</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>45977</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31408</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6757</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3651; 11613</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19132; 34779</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9798; 22084</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>827; 6668</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2347; 9424</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13082; 27268</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>10945; 23990</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1358; 9095</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>7400; 18222</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>36254; 57295</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>23628; 40278</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3150; 12482</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8707</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20645</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16337</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5157</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7780</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18734</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18876</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>16488</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>39379</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>35213</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6386</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4680; 14744</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14014; 28227</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>10814; 23333</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1937; 11141</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4003; 13601</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>12814; 25734</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12879; 26603</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3968</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>10797; 23997</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>31228; 50242</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>26594; 46303</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2813; 12096</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>15555</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>47488</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31528</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7930</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12716</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>37868</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35092</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5213</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>28271</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>85356</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>66621</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>13143</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10234; 22365</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37239; 58394</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22477; 40964</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3597; 13483</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8051; 19316</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>28717; 48243</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>26171; 44589</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2144; 10486</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>20429; 37446</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>72079; 100496</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>54592; 79978</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>8490; 21475</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/KIDM_C_3_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_3_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 10,4</t>
+          <t>3,35; 10,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,76; 23,19</t>
+          <t>13,3; 23,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 12,21</t>
+          <t>5,59; 12,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 9,82</t>
+          <t>1,1; 9,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,63</t>
+          <t>1,97; 7,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 17,72</t>
+          <t>8,53; 16,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 13,43</t>
+          <t>6,16; 13,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 9,15</t>
+          <t>1,33; 9,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,75</t>
+          <t>3,08; 7,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,93; 18,86</t>
+          <t>11,88; 18,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 11,2</t>
+          <t>6,45; 11,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,46</t>
+          <t>1,84; 7,36</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,27</t>
+          <t>2,56; 7,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 17,4</t>
+          <t>9,11; 17,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 14,16</t>
+          <t>6,24; 14,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,82</t>
+          <t>1,24; 7,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,31</t>
+          <t>2,39; 7,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 15,14</t>
+          <t>7,67; 15,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,59</t>
+          <t>7,63; 15,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,59</t>
+          <t>3,09; 6,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,4; 15,12</t>
+          <t>9,31; 14,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,93; 13,81</t>
+          <t>8,08; 13,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,85</t>
+          <t>0,98; 3,88</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,71</t>
+          <t>3,44; 7,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,93; 18,71</t>
+          <t>12,33; 18,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 11,85</t>
+          <t>6,74; 11,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,41</t>
+          <t>1,84; 6,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,24</t>
+          <t>2,46; 6,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,87; 14,9</t>
+          <t>8,91; 15,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 12,77</t>
+          <t>7,6; 12,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,87</t>
+          <t>0,79; 3,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,25</t>
+          <t>3,49; 6,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,33; 15,8</t>
+          <t>11,43; 15,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,51</t>
+          <t>7,85; 11,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,46</t>
+          <t>1,53; 4,32</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3651; 11613</t>
+          <t>3747; 12015</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19132; 34779</t>
+          <t>19946; 35680</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9798; 22084</t>
+          <t>10107; 22574</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>827; 6668</t>
+          <t>745; 6623</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2347; 9424</t>
+          <t>2437; 9852</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13082; 27268</t>
+          <t>13125; 26059</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10945; 23990</t>
+          <t>11000; 23890</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1358; 9095</t>
+          <t>1325; 9016</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7400; 18222</t>
+          <t>7238; 17452</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36254; 57295</t>
+          <t>36106; 57311</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23628; 40278</t>
+          <t>23193; 40958</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3150; 12482</t>
+          <t>3086; 12315</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4680; 14744</t>
+          <t>4572; 14197</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14014; 28227</t>
+          <t>14781; 28732</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10814; 23333</t>
+          <t>10289; 23920</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1937; 11141</t>
+          <t>1762; 10956</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4003; 13601</t>
+          <t>4445; 13357</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12814; 25734</t>
+          <t>13033; 26626</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12879; 26603</t>
+          <t>13023; 25909</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3968</t>
+          <t>0; 4508</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10797; 23997</t>
+          <t>11252; 24259</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31228; 50242</t>
+          <t>30938; 49530</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26594; 46303</t>
+          <t>27088; 46343</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2813; 12096</t>
+          <t>3067; 12194</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10234; 22365</t>
+          <t>9969; 22453</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37239; 58394</t>
+          <t>38490; 59050</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22477; 40964</t>
+          <t>23288; 41274</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3597; 13483</t>
+          <t>3869; 14270</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8051; 19316</t>
+          <t>7628; 18685</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28717; 48243</t>
+          <t>28856; 48894</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26171; 44589</t>
+          <t>26540; 45214</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2144; 10486</t>
+          <t>2142; 10620</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20429; 37446</t>
+          <t>20944; 37144</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>72079; 100496</t>
+          <t>72671; 100119</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54592; 79978</t>
+          <t>54564; 79629</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8490; 21475</t>
+          <t>7381; 20811</t>
         </is>
       </c>
     </row>
